--- a/datos/diccionario_bancos_df.xlsx
+++ b/datos/diccionario_bancos_df.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jruiz\Desktop\Work in Progress\bancos_panel\datos\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="W:\Apps\bancos_panel\datos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA2FA9D9-FAC0-4884-B62E-128D18204D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECFA4116-04D6-4E58-B0E7-BC72B2FB29D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="64">
   <si>
     <t>nombres</t>
   </si>
@@ -182,6 +182,36 @@
   </si>
   <si>
     <t>BK</t>
+  </si>
+  <si>
+    <t>Ibex</t>
+  </si>
+  <si>
+    <t>^IBEX</t>
+  </si>
+  <si>
+    <t>^STOXX50E</t>
+  </si>
+  <si>
+    <t>Eurostoxx 50</t>
+  </si>
+  <si>
+    <t>^FCHI</t>
+  </si>
+  <si>
+    <t>CAC 40</t>
+  </si>
+  <si>
+    <t>^FTSE</t>
+  </si>
+  <si>
+    <t>FTSE</t>
+  </si>
+  <si>
+    <t>FTSEMIB.MI</t>
+  </si>
+  <si>
+    <t>FTSE MIB</t>
   </si>
 </sst>
 </file>
@@ -534,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B27"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="22.90625" bestFit="1" customWidth="1"/>
@@ -756,7 +786,48 @@
         <v>53</v>
       </c>
     </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>57</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>59</v>
+      </c>
+      <c r="B30" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B32" t="s">
+        <v>62</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>